--- a/data/trans_dic/P19E_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P19E_R-Provincia-trans_dic.xlsx
@@ -514,7 +514,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se cepilla los dientes una o ninguna vez al día</t>
+          <t>Población que se cepilla los dientes una o ninguna vez al día (tasa de respuesta: 98,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>38,02; 49,91</t>
+          <t>37,86; 49,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>24,27; 35,12</t>
+          <t>23,9; 34,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16,74; 26,57</t>
+          <t>17,01; 26,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21,12; 28,85</t>
+          <t>20,66; 28,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>28,87; 36,92</t>
+          <t>29,18; 37,18</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,89; 30,48</t>
+          <t>23,85; 30,5</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>31,0; 39,22</t>
+          <t>30,87; 39,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>32,93; 43,35</t>
+          <t>33,02; 43,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20,68; 28,84</t>
+          <t>20,62; 28,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21,63; 27,91</t>
+          <t>21,59; 27,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>26,79; 32,78</t>
+          <t>27,14; 33,07</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,66; 34,59</t>
+          <t>28,43; 34,82</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,06; 12,15</t>
+          <t>6,22; 12,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>34,27; 44,84</t>
+          <t>34,2; 45,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,77; 10,65</t>
+          <t>4,72; 10,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22,25; 29,95</t>
+          <t>22,15; 29,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,19; 10,27</t>
+          <t>6,19; 10,26</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>29,11; 35,57</t>
+          <t>28,43; 35,48</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>36,15; 46,56</t>
+          <t>36,32; 46,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,61; 18,64</t>
+          <t>9,75; 18,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20,58; 29,94</t>
+          <t>20,72; 30,57</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,46; 12,45</t>
+          <t>5,78; 12,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>29,61; 36,61</t>
+          <t>29,45; 36,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,82; 13,42</t>
+          <t>7,53; 13,52</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>31,37; 44,59</t>
+          <t>31,61; 44,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,78; 4,81</t>
+          <t>0,9; 4,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22,75; 34,81</t>
+          <t>22,79; 35,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,91; 3,25</t>
+          <t>0,89; 3,23</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>28,57; 37,6</t>
+          <t>29,16; 37,92</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,12</t>
+          <t>1,11; 3,14</t>
         </is>
       </c>
     </row>
@@ -1032,32 +1032,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>58,41; 69,91</t>
+          <t>58,69; 70,53</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>40,45; 51,41</t>
+          <t>40,41; 51,11</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>46,3; 58,77</t>
+          <t>46,74; 58,39</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>31,18; 40,78</t>
+          <t>31,36; 40,59</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>54,11; 62,58</t>
+          <t>53,77; 62,56</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>37,28; 44,29</t>
+          <t>37,67; 44,55</t>
         </is>
       </c>
     </row>
@@ -1112,32 +1112,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>42,9; 51,78</t>
+          <t>43,29; 51,76</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>21,93; 30,36</t>
+          <t>21,86; 30,86</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27,94; 35,63</t>
+          <t>27,78; 35,64</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,04; 12,34</t>
+          <t>3,97; 12,27</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>36,46; 42,43</t>
+          <t>36,7; 42,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,88; 19,9</t>
+          <t>9,85; 19,56</t>
         </is>
       </c>
     </row>
@@ -1192,32 +1192,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>14,88; 19,9</t>
+          <t>14,72; 20,15</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,13; 13,95</t>
+          <t>4,65; 14,35</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11,01; 15,88</t>
+          <t>11,1; 15,98</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7,58; 11,01</t>
+          <t>7,33; 10,76</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>13,39; 17,11</t>
+          <t>13,63; 17,2</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,87; 11,58</t>
+          <t>5,94; 11,79</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>33,14; 36,55</t>
+          <t>33,11; 36,54</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>18,78; 26,57</t>
+          <t>18,67; 26,66</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>22,56; 25,24</t>
+          <t>22,52; 25,52</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12,86; 16,97</t>
+          <t>12,45; 17,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>28,14; 30,32</t>
+          <t>28,07; 30,41</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>17,03; 21,28</t>
+          <t>17,35; 21,29</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1350,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se cepilla los dientes una o ninguna vez al día</t>
+          <t>Población que se cepilla los dientes una o ninguna vez al día (tasa de respuesta: 98,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1506,32 +1506,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>109355; 143544</t>
+          <t>108880; 143743</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>75560; 109329</t>
+          <t>74398; 108608</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>47585; 75544</t>
+          <t>48356; 76225</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>60998; 83341</t>
+          <t>59687; 82887</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>165127; 211128</t>
+          <t>166878; 212646</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>143378; 182912</t>
+          <t>143110; 183067</t>
         </is>
       </c>
     </row>
@@ -1624,32 +1624,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>149713; 189425</t>
+          <t>149099; 190981</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>170709; 224707</t>
+          <t>171170; 225840</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>104734; 146046</t>
+          <t>104439; 146281</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>111122; 143373</t>
+          <t>110908; 141997</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>265064; 324352</t>
+          <t>268542; 327156</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>295795; 356944</t>
+          <t>293419; 359380</t>
         </is>
       </c>
     </row>
@@ -1742,32 +1742,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>19035; 38175</t>
+          <t>19538; 39541</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>107110; 140151</t>
+          <t>106895; 141003</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15883; 35445</t>
+          <t>15709; 35937</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>77139; 103847</t>
+          <t>76796; 103207</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>40015; 66421</t>
+          <t>40032; 66395</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>191896; 234513</t>
+          <t>187422; 233916</t>
         </is>
       </c>
     </row>
@@ -1860,32 +1860,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>132637; 170821</t>
+          <t>133268; 171968</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>29508; 57231</t>
+          <t>29943; 56678</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>79296; 115367</t>
+          <t>79824; 117787</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>25383; 57933</t>
+          <t>26900; 59784</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>222707; 275342</t>
+          <t>221492; 273927</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>60386; 103653</t>
+          <t>58129; 104407</t>
         </is>
       </c>
     </row>
@@ -1978,32 +1978,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>64552; 91772</t>
+          <t>65061; 92336</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1399; 8603</t>
+          <t>1603; 8187</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>48895; 74809</t>
+          <t>48972; 76764</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1884; 6760</t>
+          <t>1843; 6721</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>120208; 158188</t>
+          <t>122691; 159524</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4512; 12058</t>
+          <t>4302; 12122</t>
         </is>
       </c>
     </row>
@@ -2096,32 +2096,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>153139; 183297</t>
+          <t>153865; 184923</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>108758; 138237</t>
+          <t>108662; 137430</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>126025; 159976</t>
+          <t>127215; 158927</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>80149; 104830</t>
+          <t>80609; 104348</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>289168; 334429</t>
+          <t>287352; 334304</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>196079; 232966</t>
+          <t>198108; 234338</t>
         </is>
       </c>
     </row>
@@ -2214,32 +2214,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>262735; 317096</t>
+          <t>265101; 317020</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>136054; 188376</t>
+          <t>135605; 191463</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>178781; 227953</t>
+          <t>177718; 227992</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>34175; 104374</t>
+          <t>33569; 103857</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>456612; 531294</t>
+          <t>459530; 532083</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>159603; 291819</t>
+          <t>144497; 286838</t>
         </is>
       </c>
     </row>
@@ -2332,32 +2332,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>113998; 152392</t>
+          <t>112733; 154347</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>38344; 129517</t>
+          <t>43125; 133141</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>90263; 130211</t>
+          <t>91040; 130994</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>54247; 78777</t>
+          <t>52422; 76974</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>212320; 271361</t>
+          <t>216130; 272711</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>96415; 190373</t>
+          <t>97554; 193812</t>
         </is>
       </c>
     </row>
@@ -2450,32 +2450,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>1092862; 1205256</t>
+          <t>1091847; 1204950</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>647156; 915610</t>
+          <t>643385; 918610</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>779455; 872098</t>
+          <t>778291; 881775</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>468059; 617864</t>
+          <t>453223; 618795</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1900490; 2047522</t>
+          <t>1895627; 2053835</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1206988; 1507856</t>
+          <t>1229740; 1508502</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19E_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P19E_R-Provincia-trans_dic.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>31,01%</t>
         </is>
       </c>
     </row>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>37,86; 49,98</t>
+          <t>37,43; 50,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>23,9; 34,89</t>
+          <t>29,63; 40,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17,01; 26,81</t>
+          <t>16,61; 26,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20,66; 28,69</t>
+          <t>23,09; 30,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>29,18; 37,18</t>
+          <t>29,3; 36,88</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,85; 30,5</t>
+          <t>27,92; 34,54</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,5%</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>30,87; 39,55</t>
+          <t>30,95; 39,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>33,02; 43,57</t>
+          <t>32,83; 43,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20,62; 28,88</t>
+          <t>20,83; 28,75</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21,59; 27,64</t>
+          <t>21,92; 28,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>27,14; 33,07</t>
+          <t>26,72; 32,88</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,43; 34,82</t>
+          <t>28,52; 34,46</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>39,41%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>32,53%</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,22; 12,59</t>
+          <t>6,02; 12,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>34,2; 45,12</t>
+          <t>34,46; 44,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,72; 10,8</t>
+          <t>4,91; 10,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22,15; 29,77</t>
+          <t>23,17; 30,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,19; 10,26</t>
+          <t>6,12; 10,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>28,43; 35,48</t>
+          <t>29,26; 35,77</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>12,19%</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>36,32; 46,87</t>
+          <t>36,54; 46,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,75; 18,46</t>
+          <t>9,37; 17,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20,72; 30,57</t>
+          <t>20,97; 30,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,78; 12,85</t>
+          <t>9,11; 14,97</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>29,45; 36,42</t>
+          <t>29,69; 36,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,53; 13,52</t>
+          <t>10,05; 15,2</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>31,61; 44,87</t>
+          <t>31,53; 44,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,9; 4,58</t>
+          <t>0,7; 3,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22,79; 35,72</t>
+          <t>22,68; 35,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,89; 3,23</t>
+          <t>0,94; 3,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>29,16; 37,92</t>
+          <t>28,59; 37,71</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,11; 3,14</t>
+          <t>1,09; 3,01</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>45,88%</t>
+          <t>47,62%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>41,98%</t>
         </is>
       </c>
     </row>
@@ -1032,32 +1032,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>58,69; 70,53</t>
+          <t>58,54; 70,19</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>40,41; 51,11</t>
+          <t>42,48; 53,01</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>46,74; 58,39</t>
+          <t>46,46; 58,54</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>31,36; 40,59</t>
+          <t>31,68; 40,63</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>53,77; 62,56</t>
+          <t>54,01; 62,6</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>37,67; 44,55</t>
+          <t>38,51; 45,88</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>17,13%</t>
         </is>
       </c>
     </row>
@@ -1112,32 +1112,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>43,29; 51,76</t>
+          <t>43,3; 51,83</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>21,86; 30,86</t>
+          <t>20,43; 27,6</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27,78; 35,64</t>
+          <t>28,09; 35,6</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,97; 12,27</t>
+          <t>9,05; 13,09</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>36,7; 42,49</t>
+          <t>36,7; 42,26</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,85; 19,56</t>
+          <t>15,05; 19,2</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>11,04%</t>
         </is>
       </c>
     </row>
@@ -1192,32 +1192,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>14,72; 20,15</t>
+          <t>14,93; 20,35</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,65; 14,35</t>
+          <t>10,69; 15,34</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11,1; 15,98</t>
+          <t>11,12; 16,07</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7,33; 10,76</t>
+          <t>7,69; 11,26</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>13,63; 17,2</t>
+          <t>13,65; 17,24</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,94; 11,79</t>
+          <t>9,67; 12,52</t>
         </is>
       </c>
     </row>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>20,92%</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>33,11; 36,54</t>
+          <t>33,07; 36,4</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>18,67; 26,66</t>
+          <t>23,71; 26,88</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>22,52; 25,52</t>
+          <t>22,62; 25,47</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12,45; 17,0</t>
+          <t>15,74; 17,88</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>28,07; 30,41</t>
+          <t>28,13; 30,36</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>17,35; 21,29</t>
+          <t>20,02; 21,83</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>91278</t>
+          <t>111716</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>71439</t>
+          <t>84648</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>162717</t>
+          <t>196364</t>
         </is>
       </c>
     </row>
@@ -1506,32 +1506,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>108880; 143743</t>
+          <t>107644; 143961</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>74398; 108608</t>
+          <t>94198; 128549</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>48356; 76225</t>
+          <t>47232; 75437</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>59687; 82887</t>
+          <t>72808; 97641</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>166878; 212646</t>
+          <t>167582; 210929</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>143110; 183067</t>
+          <t>176812; 218764</t>
         </is>
       </c>
     </row>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>197820</t>
+          <t>202765</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>126605</t>
+          <t>135865</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>324425</t>
+          <t>338630</t>
         </is>
       </c>
     </row>
@@ -1624,32 +1624,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>149099; 190981</t>
+          <t>149445; 192432</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>171170; 225840</t>
+          <t>174227; 230133</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>104439; 146281</t>
+          <t>105471; 145594</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>110908; 141997</t>
+          <t>119379; 153820</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>268542; 327156</t>
+          <t>264335; 325345</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>293419; 359380</t>
+          <t>306613; 370487</t>
         </is>
       </c>
     </row>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>122897</t>
+          <t>123228</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>89303</t>
+          <t>93648</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>212200</t>
+          <t>216877</t>
         </is>
       </c>
     </row>
@@ -1742,32 +1742,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>19538; 39541</t>
+          <t>18916; 39315</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>106895; 141003</t>
+          <t>107749; 140409</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15709; 35937</t>
+          <t>16346; 35723</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>76796; 103207</t>
+          <t>81994; 107460</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>40032; 66395</t>
+          <t>39571; 67596</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>187422; 233916</t>
+          <t>195023; 238452</t>
         </is>
       </c>
     </row>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>40990</t>
+          <t>47420</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>42588</t>
+          <t>47224</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83578</t>
+          <t>94644</t>
         </is>
       </c>
     </row>
@@ -1860,32 +1860,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>133268; 171968</t>
+          <t>134063; 171916</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>29943; 56678</t>
+          <t>34266; 65273</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>79824; 117787</t>
+          <t>80779; 117402</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>26900; 59784</t>
+          <t>37389; 61471</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>221492; 273927</t>
+          <t>223299; 275492</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>58129; 104407</t>
+          <t>77991; 118003</t>
         </is>
       </c>
     </row>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3685</t>
+          <t>3985</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3806</t>
+          <t>3998</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7491</t>
+          <t>7983</t>
         </is>
       </c>
     </row>
@@ -1978,32 +1978,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>65061; 92336</t>
+          <t>64893; 91833</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1603; 8187</t>
+          <t>1439; 8158</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>48972; 76764</t>
+          <t>48734; 76751</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1843; 6721</t>
+          <t>2135; 7062</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>122691; 159524</t>
+          <t>120275; 158633</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4302; 12122</t>
+          <t>4718; 12985</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>123364</t>
+          <t>128552</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>91559</t>
+          <t>95515</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>214922</t>
+          <t>224067</t>
         </is>
       </c>
     </row>
@@ -2096,32 +2096,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>153865; 184923</t>
+          <t>153470; 184021</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>108662; 137430</t>
+          <t>114692; 143127</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>127215; 158927</t>
+          <t>126455; 159346</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>80609; 104348</t>
+          <t>83568; 107169</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>287352; 334304</t>
+          <t>288589; 334539</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>198108; 234338</t>
+          <t>205556; 244854</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>160658</t>
+          <t>170113</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>74418</t>
+          <t>83923</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>235077</t>
+          <t>254036</t>
         </is>
       </c>
     </row>
@@ -2214,32 +2214,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>265101; 317020</t>
+          <t>265209; 317451</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>135605; 191463</t>
+          <t>146136; 197402</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>177718; 227992</t>
+          <t>179698; 227773</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>33569; 103857</t>
+          <t>69461; 100439</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>459530; 532083</t>
+          <t>459622; 529219</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>144497; 286838</t>
+          <t>223196; 284729</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>90668</t>
+          <t>102241</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -2309,7 +2309,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>65597</t>
+          <t>77486</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>156265</t>
+          <t>179727</t>
         </is>
       </c>
     </row>
@@ -2332,32 +2332,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>112733; 154347</t>
+          <t>114341; 155895</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>43125; 133141</t>
+          <t>85207; 122352</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>91040; 130994</t>
+          <t>91182; 131813</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>52422; 76974</t>
+          <t>63906; 93547</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>216130; 272711</t>
+          <t>216447; 273454</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>97554; 193812</t>
+          <t>157393; 203799</t>
         </is>
       </c>
     </row>
@@ -2417,7 +2417,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>831359</t>
+          <t>890020</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>565315</t>
+          <t>622307</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1396675</t>
+          <t>1512326</t>
         </is>
       </c>
     </row>
@@ -2450,32 +2450,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>1091847; 1204950</t>
+          <t>1090513; 1200348</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>643385; 918610</t>
+          <t>833545; 944961</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>778291; 881775</t>
+          <t>781514; 880129</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>453223; 618795</t>
+          <t>584212; 663759</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1895627; 2053835</t>
+          <t>1899530; 2050258</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1229740; 1508502</t>
+          <t>1447161; 1578159</t>
         </is>
       </c>
     </row>
